--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty 100 ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty 100 ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="276">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty 100 ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -103,28 +103,34 @@
     <t>Telecom - Services</t>
   </si>
   <si>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
     <t>Tata Consultancy Services Ltd.</t>
   </si>
   <si>
     <t>INE467B01029</t>
   </si>
   <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
   </si>
   <si>
     <t>State Bank Of India</t>
@@ -133,12 +139,6 @@
     <t>INE062A01020</t>
   </si>
   <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
     <t>Kotak Mahindra Bank Ltd.</t>
   </si>
   <si>
@@ -184,6 +184,15 @@
     <t>INE860A01027</t>
   </si>
   <si>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
     <t>Maruti Suzuki India Ltd.</t>
   </si>
   <si>
@@ -199,15 +208,6 @@
     <t>Power</t>
   </si>
   <si>
-    <t>Zomato Ltd.</t>
-  </si>
-  <si>
-    <t>INE758T01015</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
     <t>Tata Motors Ltd.</t>
   </si>
   <si>
@@ -223,6 +223,24 @@
     <t>Consumer Durables</t>
   </si>
   <si>
+    <t>Bharat Electronics Ltd.</t>
+  </si>
+  <si>
+    <t>INE263A01024</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
     <t>Power Grid Corporation Of India Ltd.</t>
   </si>
   <si>
@@ -244,13 +262,34 @@
     <t>INE849A01020</t>
   </si>
   <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
+    <t>Bajaj Finserv Ltd.</t>
+  </si>
+  <si>
+    <t>INE918I01026</t>
+  </si>
+  <si>
+    <t>Adani Ports and Special Economic Zone Ltd.</t>
+  </si>
+  <si>
+    <t>INE742F01042</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>Asian Paints Ltd.</t>
+  </si>
+  <si>
+    <t>INE021A01026</t>
   </si>
   <si>
     <t>Tech Mahindra Ltd.</t>
@@ -259,19 +298,34 @@
     <t>INE669C01036</t>
   </si>
   <si>
-    <t>Bharat Electronics Ltd.</t>
-  </si>
-  <si>
-    <t>INE263A01024</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>Asian Paints Ltd.</t>
-  </si>
-  <si>
-    <t>INE021A01026</t>
+    <t>Grasim Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE047A01021</t>
+  </si>
+  <si>
+    <t>Bajaj Auto Ltd.</t>
+  </si>
+  <si>
+    <t>INE917I01010</t>
+  </si>
+  <si>
+    <t>Hindustan Aeronautics Ltd.</t>
+  </si>
+  <si>
+    <t>INE066F01020</t>
+  </si>
+  <si>
+    <t>JSW Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE019A01038</t>
+  </si>
+  <si>
+    <t>Jio Financial Services Ltd</t>
+  </si>
+  <si>
+    <t>INE758E01017</t>
   </si>
   <si>
     <t>Oil &amp; Natural Gas Corporation Ltd.</t>
@@ -283,28 +337,13 @@
     <t>Oil</t>
   </si>
   <si>
-    <t>Bajaj Auto Ltd.</t>
-  </si>
-  <si>
-    <t>INE917I01010</t>
-  </si>
-  <si>
-    <t>Bajaj Finserv Ltd.</t>
-  </si>
-  <si>
-    <t>INE918I01026</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>JSW Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE019A01038</t>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
   </si>
   <si>
     <t>Coal India Ltd.</t>
@@ -316,85 +355,133 @@
     <t>Consumable Fuels</t>
   </si>
   <si>
+    <t>Shriram Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE721A01047</t>
+  </si>
+  <si>
+    <t>Nestle India Ltd.</t>
+  </si>
+  <si>
+    <t>INE239A01024</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
+    <t>Divi's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE361B01024</t>
+  </si>
+  <si>
+    <t>HDFC Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE795G01014</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Cipla Ltd.</t>
+  </si>
+  <si>
+    <t>INE059A01026</t>
+  </si>
+  <si>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
+  </si>
+  <si>
+    <t>Eicher Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE066A01021</t>
+  </si>
+  <si>
+    <t>Tata Consumer Products Ltd.</t>
+  </si>
+  <si>
+    <t>INE192A01025</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
     <t>Wipro Ltd.</t>
   </si>
   <si>
     <t>INE075A01022</t>
   </si>
   <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>Nestle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE239A01024</t>
-  </si>
-  <si>
-    <t>Food Products</t>
-  </si>
-  <si>
-    <t>Cipla Ltd.</t>
-  </si>
-  <si>
-    <t>INE059A01026</t>
-  </si>
-  <si>
-    <t>Adani Ports and Special Economic Zone Ltd.</t>
-  </si>
-  <si>
-    <t>INE742F01042</t>
-  </si>
-  <si>
-    <t>Transport Infrastructure</t>
-  </si>
-  <si>
-    <t>Jio Financial Services Ltd</t>
-  </si>
-  <si>
-    <t>INE758E01017</t>
-  </si>
-  <si>
-    <t>Shriram Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE721A01047</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
-  </si>
-  <si>
-    <t>Hindustan Aeronautics Ltd.</t>
-  </si>
-  <si>
-    <t>INE066F01020</t>
-  </si>
-  <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
+    <t>Apollo Hospitals Enterprise Ltd.</t>
+  </si>
+  <si>
+    <t>INE437A01024</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
+    <t>The Indian Hotels Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE053A01029</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
+  </si>
+  <si>
+    <t>Cholamandalam Investment And Finance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE121A01024</t>
+  </si>
+  <si>
+    <t>Tata Power Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE245A01021</t>
+  </si>
+  <si>
+    <t>Adani Enterprises Ltd.</t>
+  </si>
+  <si>
+    <t>INE423A01024</t>
+  </si>
+  <si>
+    <t>Metals &amp; Minerals Trading</t>
+  </si>
+  <si>
+    <t>TVS Motor Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE494B01023</t>
+  </si>
+  <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
   </si>
   <si>
     <t>Varun Beverages Ltd.</t>
@@ -406,49 +493,49 @@
     <t>Beverages</t>
   </si>
   <si>
-    <t>Eicher Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE066A01021</t>
-  </si>
-  <si>
-    <t>Divi's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE361B01024</t>
-  </si>
-  <si>
-    <t>Apollo Hospitals Enterprise Ltd.</t>
-  </si>
-  <si>
-    <t>INE437A01024</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
-    <t>HDFC Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE795G01014</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>Tata Consumer Products Ltd.</t>
-  </si>
-  <si>
-    <t>INE192A01025</t>
-  </si>
-  <si>
-    <t>Agricultural Food &amp; Other Products</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
+    <t>Bharat Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE029A01011</t>
+  </si>
+  <si>
+    <t>Power Finance Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE134E01011</t>
+  </si>
+  <si>
+    <t>Godrej Consumer Products Ltd.</t>
+  </si>
+  <si>
+    <t>INE102D01028</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Avenue Supermarts Ltd.</t>
+  </si>
+  <si>
+    <t>INE192R01011</t>
+  </si>
+  <si>
+    <t>Bajaj Holdings &amp; Investment Ltd.</t>
+  </si>
+  <si>
+    <t>INE118A01012</t>
+  </si>
+  <si>
+    <t>Hero Motocorp Ltd.</t>
+  </si>
+  <si>
+    <t>INE158A01026</t>
+  </si>
+  <si>
+    <t>Info Edge (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE663F01032</t>
   </si>
   <si>
     <t>IndusInd Bank Ltd.</t>
@@ -457,49 +544,28 @@
     <t>INE095A01012</t>
   </si>
   <si>
-    <t>Tata Power Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE245A01021</t>
-  </si>
-  <si>
-    <t>Power Finance Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE134E01011</t>
-  </si>
-  <si>
-    <t>Info Edge (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE663F01024</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
-    <t>TVS Motor Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE494B01023</t>
-  </si>
-  <si>
-    <t>Adani Enterprises Ltd.</t>
-  </si>
-  <si>
-    <t>INE423A01024</t>
-  </si>
-  <si>
-    <t>Metals &amp; Minerals Trading</t>
-  </si>
-  <si>
-    <t>Hero Motocorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE158A01026</t>
+    <t>Indian Oil Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE242A01010</t>
+  </si>
+  <si>
+    <t>GAIL (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE129A01019</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>DLF Ltd.</t>
+  </si>
+  <si>
+    <t>INE271C01023</t>
+  </si>
+  <si>
+    <t>Realty</t>
   </si>
   <si>
     <t>Rural Electrification Corporation Ltd.</t>
@@ -508,22 +574,127 @@
     <t>INE020B01018</t>
   </si>
   <si>
+    <t>Pidilite Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE318A01026</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
     <t>LTIMindtree Ltd.</t>
   </si>
   <si>
     <t>INE214T01019</t>
   </si>
   <si>
-    <t>Avenue Supermarts Ltd.</t>
-  </si>
-  <si>
-    <t>INE192R01011</t>
-  </si>
-  <si>
-    <t>Cholamandalam Investment And Finance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE121A01024</t>
+    <t>Bank Of Baroda</t>
+  </si>
+  <si>
+    <t>INE028A01039</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd.</t>
+  </si>
+  <si>
+    <t>INE775A01035</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>United Spirits Ltd.</t>
+  </si>
+  <si>
+    <t>INE854D01024</t>
+  </si>
+  <si>
+    <t>ICICI Lombard General Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE765G01017</t>
+  </si>
+  <si>
+    <t>CG Power and Industrial Solutions Ltd.</t>
+  </si>
+  <si>
+    <t>INE067A01029</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
+    <t>Adani Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE814H01011</t>
+  </si>
+  <si>
+    <t>Macrotech Developers Ltd.</t>
+  </si>
+  <si>
+    <t>INE670K01029</t>
+  </si>
+  <si>
+    <t>Shree Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE070A01015</t>
+  </si>
+  <si>
+    <t>Canara Bank</t>
+  </si>
+  <si>
+    <t>INE476A01022</t>
+  </si>
+  <si>
+    <t>Havells India Ltd.</t>
+  </si>
+  <si>
+    <t>INE176B01034</t>
+  </si>
+  <si>
+    <t>Ambuja Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE079A01024</t>
+  </si>
+  <si>
+    <t>Punjab National Bank</t>
+  </si>
+  <si>
+    <t>INE160A01022</t>
+  </si>
+  <si>
+    <t>Jindal Steel &amp; Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE749A01030</t>
+  </si>
+  <si>
+    <t>Torrent Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE685A01028</t>
+  </si>
+  <si>
+    <t>Adani Energy Solutions Ltd.</t>
+  </si>
+  <si>
+    <t>INE931S01010</t>
+  </si>
+  <si>
+    <t>ABB India Ltd.</t>
+  </si>
+  <si>
+    <t>INE117A01022</t>
+  </si>
+  <si>
+    <t>Adani Green Energy Ltd.</t>
+  </si>
+  <si>
+    <t>INE364U01010</t>
   </si>
   <si>
     <t>Siemens Ltd.</t>
@@ -532,160 +703,16 @@
     <t>INE003A01024</t>
   </si>
   <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>Bajaj Holdings &amp; Investment Ltd.</t>
-  </si>
-  <si>
-    <t>INE118A01012</t>
-  </si>
-  <si>
-    <t>Indian Oil Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE242A01010</t>
-  </si>
-  <si>
-    <t>GAIL (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE129A01019</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>DLF Ltd.</t>
-  </si>
-  <si>
-    <t>INE271C01023</t>
-  </si>
-  <si>
-    <t>Realty</t>
-  </si>
-  <si>
-    <t>ICICI Lombard General Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE765G01017</t>
-  </si>
-  <si>
-    <t>Pidilite Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE318A01026</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>Godrej Consumer Products Ltd.</t>
-  </si>
-  <si>
-    <t>INE102D01028</t>
-  </si>
-  <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
-    <t>United Spirits Ltd.</t>
-  </si>
-  <si>
-    <t>INE854D01024</t>
-  </si>
-  <si>
-    <t>Samvardhana Motherson International Ltd.</t>
-  </si>
-  <si>
-    <t>INE775A01035</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Adani Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE814H01011</t>
-  </si>
-  <si>
-    <t>Bank Of Baroda</t>
-  </si>
-  <si>
-    <t>INE028A01039</t>
-  </si>
-  <si>
-    <t>Havells India Ltd.</t>
-  </si>
-  <si>
-    <t>INE176B01034</t>
-  </si>
-  <si>
-    <t>Shree Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE070A01015</t>
-  </si>
-  <si>
-    <t>Punjab National Bank</t>
-  </si>
-  <si>
-    <t>INE160A01022</t>
-  </si>
-  <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>Macrotech Developers Ltd.</t>
-  </si>
-  <si>
-    <t>INE670K01029</t>
-  </si>
-  <si>
-    <t>Canara Bank</t>
-  </si>
-  <si>
-    <t>INE476A01022</t>
-  </si>
-  <si>
     <t>Dabur India Ltd.</t>
   </si>
   <si>
     <t>INE016A01026</t>
   </si>
   <si>
-    <t>ABB India Ltd.</t>
-  </si>
-  <si>
-    <t>INE117A01022</t>
-  </si>
-  <si>
-    <t>Torrent Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE685A01028</t>
-  </si>
-  <si>
-    <t>Adani Green Energy Ltd.</t>
-  </si>
-  <si>
-    <t>INE364U01010</t>
-  </si>
-  <si>
-    <t>Jindal Steel &amp; Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE749A01030</t>
+    <t>Bosch Ltd.</t>
+  </si>
+  <si>
+    <t>INE323A01026</t>
   </si>
   <si>
     <t>JSW Energy Ltd</t>
@@ -694,10 +721,10 @@
     <t>INE121E01018</t>
   </si>
   <si>
-    <t>Adani Energy Solutions Ltd.</t>
-  </si>
-  <si>
-    <t>INE931S01010</t>
+    <t>ICICI Prudential Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE726G01019</t>
   </si>
   <si>
     <t>Indian Railway Finance Corporation Ltd.</t>
@@ -706,49 +733,22 @@
     <t>INE053F01010</t>
   </si>
   <si>
-    <t>Bharat Heavy Electricals Ltd.</t>
-  </si>
-  <si>
-    <t>INE257A01026</t>
-  </si>
-  <si>
-    <t>NHPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE848E01016</t>
-  </si>
-  <si>
-    <t>Indian Railway Catering and Tourism Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE335Y01020</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>Bosch Ltd.</t>
-  </si>
-  <si>
-    <t>INE323A01026</t>
-  </si>
-  <si>
     <t>Zydus Lifesciences Ltd.</t>
   </si>
   <si>
     <t>INE010B01027</t>
   </si>
   <si>
-    <t>ICICI Prudential Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE726G01019</t>
-  </si>
-  <si>
-    <t>Union Bank Of India</t>
-  </si>
-  <si>
-    <t>INE692A01016</t>
+    <t>Hyundai Motor India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0V6F01027</t>
+  </si>
+  <si>
+    <t>SIEMENS ENERGY INDIA LTD</t>
+  </si>
+  <si>
+    <t>INE1NPP01017</t>
   </si>
   <si>
     <t>Life Insurance Corporation of India</t>
@@ -757,16 +757,16 @@
     <t>INE0J1Y01017</t>
   </si>
   <si>
-    <t>Adani total gas Ltd.</t>
-  </si>
-  <si>
-    <t>INE399L01023</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
+    <t>Swiggy Ltd</t>
+  </si>
+  <si>
+    <t>INE00H001014</t>
+  </si>
+  <si>
+    <t>Bajaj Housing Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE377Y01014</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -814,25 +814,19 @@
     <t>Net Current Assets</t>
   </si>
   <si>
-    <t>^</t>
-  </si>
-  <si>
     <t>Total Net Assets</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
-    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
-  </si>
-  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1118,10 +1112,10 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1218,13 +1212,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>154</xdr:row>
+      <xdr:row>153</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>164</xdr:row>
+      <xdr:row>163</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1242,7 +1236,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="29946600"/>
+          <a:off x="666750" y="29756100"/>
           <a:ext cx="3810000" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1257,13 +1251,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>169</xdr:row>
+      <xdr:row>168</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>179</xdr:row>
+      <xdr:row>178</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1281,7 +1275,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="32804100"/>
+          <a:off x="666750" y="32613600"/>
           <a:ext cx="3810000" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1615,7 +1609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J168"/>
+  <dimension ref="B1:J167"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1715,10 +1709,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>10767.76</v>
+        <v>11771.820000000007</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9997123603688995</v>
+        <v>0.9986510161922998</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1752,10 +1746,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>10767.76</v>
+        <v>11771.820000000007</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9997123603688995</v>
+        <v>0.9986510161922998</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1778,13 +1772,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>63879</v>
+        <v>66164</v>
       </c>
       <c r="G8" s="15">
-        <v>1085.14</v>
+        <v>1286.82</v>
       </c>
       <c r="H8" s="16">
-        <v>0.100747775836</v>
+        <v>0.109166135794</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1807,13 +1801,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>59273</v>
+        <v>61390</v>
       </c>
       <c r="G9" s="15">
-        <v>742.57</v>
+        <v>887.58</v>
       </c>
       <c r="H9" s="16">
-        <v>0.068942510554</v>
+        <v>0.0752969947685</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1836,13 +1830,13 @@
         <v>22</v>
       </c>
       <c r="F10" s="14">
-        <v>57026</v>
+        <v>58928</v>
       </c>
       <c r="G10" s="15">
-        <v>721.44</v>
+        <v>837.31</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0669807355725</v>
+        <v>0.0710323877167</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1865,13 +1859,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="14">
-        <v>30259</v>
+        <v>31310</v>
       </c>
       <c r="G11" s="15">
-        <v>568.81</v>
+        <v>489.28</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0528100912078</v>
+        <v>0.041507597738</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1894,13 +1888,13 @@
         <v>28</v>
       </c>
       <c r="F12" s="14">
-        <v>22530</v>
+        <v>23333</v>
       </c>
       <c r="G12" s="15">
-        <v>366.41</v>
+        <v>433.11</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0340186451002</v>
+        <v>0.0367424698666</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1920,16 +1914,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F13" s="14">
-        <v>8584</v>
+        <v>10210</v>
       </c>
       <c r="G13" s="15">
-        <v>353.01</v>
+        <v>375.23</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0327745473836</v>
+        <v>0.0318322757914</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1940,25 +1934,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F14" s="14">
-        <v>9889</v>
+        <v>80962</v>
       </c>
       <c r="G14" s="15">
-        <v>352.78</v>
+        <v>338.46</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0327531934676</v>
+        <v>0.0287129282423</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1969,25 +1963,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F15" s="14">
-        <v>78102</v>
+        <v>8882</v>
       </c>
       <c r="G15" s="15">
-        <v>349.51</v>
+        <v>307.62</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0324495964875</v>
+        <v>0.026096646534</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -2010,13 +2004,13 @@
         <v>17</v>
       </c>
       <c r="F16" s="14">
-        <v>32327</v>
+        <v>24853</v>
       </c>
       <c r="G16" s="15">
-        <v>249.86</v>
+        <v>296.30</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0231977802591</v>
+        <v>0.0251363252325</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -2039,13 +2033,13 @@
         <v>17</v>
       </c>
       <c r="F17" s="14">
-        <v>23956</v>
+        <v>33415</v>
       </c>
       <c r="G17" s="15">
-        <v>236.23</v>
+        <v>271.43</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0219323286264</v>
+        <v>0.0230265027265</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -2068,13 +2062,13 @@
         <v>17</v>
       </c>
       <c r="F18" s="14">
-        <v>12335</v>
+        <v>12788</v>
       </c>
       <c r="G18" s="15">
-        <v>234.53</v>
+        <v>265.31</v>
       </c>
       <c r="H18" s="16">
-        <v>0.021774495334</v>
+        <v>0.0225073184186</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -2097,13 +2091,13 @@
         <v>45</v>
       </c>
       <c r="F19" s="14">
-        <v>7437</v>
+        <v>7707</v>
       </c>
       <c r="G19" s="15">
-        <v>222.36</v>
+        <v>229.42</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0206445946466</v>
+        <v>0.0194626248223</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -2126,13 +2120,13 @@
         <v>48</v>
       </c>
       <c r="F20" s="14">
-        <v>2351</v>
+        <v>2274</v>
       </c>
       <c r="G20" s="15">
-        <v>185.38</v>
+        <v>208.76</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0172112563212</v>
+        <v>0.017709953613</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -2152,16 +2146,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F21" s="14">
-        <v>7457</v>
+        <v>7719</v>
       </c>
       <c r="G21" s="15">
-        <v>184.10</v>
+        <v>181.27</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0170924171364</v>
+        <v>0.0153778659294</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2184,13 +2178,13 @@
         <v>53</v>
       </c>
       <c r="F22" s="14">
-        <v>9067</v>
+        <v>9377</v>
       </c>
       <c r="G22" s="15">
-        <v>158.12</v>
+        <v>157.31</v>
       </c>
       <c r="H22" s="16">
-        <v>0.014680353056</v>
+        <v>0.0133452423973</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2213,13 +2207,13 @@
         <v>25</v>
       </c>
       <c r="F23" s="14">
-        <v>8892</v>
+        <v>9225</v>
       </c>
       <c r="G23" s="15">
-        <v>153.43</v>
+        <v>150.98</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0142449188551</v>
+        <v>0.0128082429416</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2239,16 +2233,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F24" s="14">
-        <v>1105</v>
+        <v>60425</v>
       </c>
       <c r="G24" s="15">
-        <v>136.03</v>
+        <v>144</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0126294486858</v>
+        <v>0.0122161013617</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2259,25 +2253,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F25" s="14">
-        <v>39776</v>
+        <v>1141</v>
       </c>
       <c r="G25" s="15">
-        <v>128.87</v>
+        <v>140.56</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0119646919954</v>
+        <v>0.0119242722736</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2300,13 +2294,13 @@
         <v>63</v>
       </c>
       <c r="F26" s="14">
-        <v>58235</v>
+        <v>41241</v>
       </c>
       <c r="G26" s="15">
-        <v>128.32</v>
+        <v>137.7</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0119136282832</v>
+        <v>0.0116816469271</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2329,13 +2323,13 @@
         <v>45</v>
       </c>
       <c r="F27" s="14">
-        <v>17608</v>
+        <v>18150</v>
       </c>
       <c r="G27" s="15">
-        <v>126.09</v>
+        <v>130.59</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0117065881408</v>
+        <v>0.0110784769224</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2358,13 +2352,13 @@
         <v>68</v>
       </c>
       <c r="F28" s="14">
-        <v>3475</v>
+        <v>3587</v>
       </c>
       <c r="G28" s="15">
-        <v>121.29</v>
+        <v>127.52</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0112609411975</v>
+        <v>0.0108180364281</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2384,16 +2378,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F29" s="14">
-        <v>38052</v>
+        <v>31149</v>
       </c>
       <c r="G29" s="15">
-        <v>114.78</v>
+        <v>119.80</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0106565325307</v>
+        <v>0.0101631176606</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2404,25 +2398,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F30" s="14">
-        <v>958</v>
+        <v>71920</v>
       </c>
       <c r="G30" s="15">
-        <v>110.05</v>
+        <v>115.81</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0102173846054</v>
+        <v>0.0098246298521</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2433,10 +2427,10 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
@@ -2445,13 +2439,13 @@
         <v>63</v>
       </c>
       <c r="F31" s="14">
-        <v>1865</v>
+        <v>39419</v>
       </c>
       <c r="G31" s="15">
-        <v>107.30</v>
+        <v>114.22</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0099620660442</v>
+        <v>0.0096897437329</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2462,25 +2456,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F32" s="14">
-        <v>69607</v>
+        <v>1011</v>
       </c>
       <c r="G32" s="15">
-        <v>93.70</v>
+        <v>113.33</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0086993997049</v>
+        <v>0.0096142414397</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2491,25 +2485,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F33" s="14">
-        <v>5332</v>
+        <v>1932</v>
       </c>
       <c r="G33" s="15">
-        <v>89.28</v>
+        <v>109.03</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0082890331447</v>
+        <v>0.0092494550796</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2520,25 +2514,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="F34" s="14">
-        <v>30043</v>
+        <v>4731</v>
       </c>
       <c r="G34" s="15">
-        <v>87.92</v>
+        <v>95.44</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0081627665107</v>
+        <v>0.0080965605136</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2558,16 +2552,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="F35" s="14">
-        <v>3799</v>
+        <v>6418</v>
       </c>
       <c r="G35" s="15">
-        <v>87.41</v>
+        <v>91.96</v>
       </c>
       <c r="H35" s="16">
-        <v>0.008115416523</v>
+        <v>0.007801338064</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2578,25 +2572,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F36" s="14">
-        <v>32583</v>
+        <v>1706</v>
       </c>
       <c r="G36" s="15">
-        <v>85.57</v>
+        <v>90.93</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0079445851948</v>
+        <v>0.0077139590057</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2607,25 +2601,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="F37" s="14">
-        <v>932</v>
+        <v>3934</v>
       </c>
       <c r="G37" s="15">
-        <v>82.46</v>
+        <v>88.87</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0076558431128</v>
+        <v>0.007539200889</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2636,25 +2630,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F38" s="14">
-        <v>4594</v>
+        <v>5516</v>
       </c>
       <c r="G38" s="15">
-        <v>79.76</v>
+        <v>86.82</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0074051667072</v>
+        <v>0.0073652911126</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2665,25 +2659,25 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F39" s="14">
-        <v>3121</v>
+        <v>3338</v>
       </c>
       <c r="G39" s="15">
-        <v>78.30</v>
+        <v>84.98</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0072696157619</v>
+        <v>0.0072091964841</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2694,25 +2688,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="F40" s="14">
-        <v>8061</v>
+        <v>964</v>
       </c>
       <c r="G40" s="15">
-        <v>76.18</v>
+        <v>82.97</v>
       </c>
       <c r="H40" s="16">
-        <v>0.007072788362</v>
+        <v>0.0070386800693</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2723,25 +2717,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="F41" s="14">
-        <v>19053</v>
+        <v>1652</v>
       </c>
       <c r="G41" s="15">
-        <v>75.43</v>
+        <v>82.17</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0070031560271</v>
+        <v>0.0069708128395</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2761,16 +2755,16 @@
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="F42" s="14">
-        <v>23786</v>
+        <v>8251</v>
       </c>
       <c r="G42" s="15">
-        <v>74.19</v>
+        <v>81.97</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0068880305668</v>
+        <v>0.0069538460321</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2790,16 +2784,16 @@
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="F43" s="14">
-        <v>12211</v>
+        <v>28489</v>
       </c>
       <c r="G43" s="15">
-        <v>72.57</v>
+        <v>81.66</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0067376247234</v>
+        <v>0.0069275474805</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2810,25 +2804,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="D44" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D44" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>107</v>
-      </c>
       <c r="F44" s="14">
-        <v>1647</v>
+        <v>33782</v>
       </c>
       <c r="G44" s="15">
-        <v>71.22</v>
+        <v>80.87</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0066122865206</v>
+        <v>0.0068605285911</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2839,25 +2833,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="D45" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>110</v>
-      </c>
       <c r="F45" s="14">
-        <v>3008</v>
+        <v>12592</v>
       </c>
       <c r="G45" s="15">
-        <v>69.58</v>
+        <v>79.77</v>
       </c>
       <c r="H45" s="16">
-        <v>0.006460023815</v>
+        <v>0.0067672111501</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2868,25 +2862,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="D46" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D46" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>53</v>
-      </c>
       <c r="F46" s="14">
-        <v>4617</v>
+        <v>19755</v>
       </c>
       <c r="G46" s="15">
-        <v>68.30</v>
+        <v>78.49</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0063411846301</v>
+        <v>0.0066586235825</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2906,16 +2900,16 @@
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="F47" s="14">
-        <v>6191</v>
+        <v>12173</v>
       </c>
       <c r="G47" s="15">
-        <v>68.06</v>
+        <v>77.83</v>
       </c>
       <c r="H47" s="16">
-        <v>0.006318902283</v>
+        <v>0.0066026331179</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2926,25 +2920,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="D48" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D48" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>48</v>
-      </c>
       <c r="F48" s="14">
-        <v>27562</v>
+        <v>3118</v>
       </c>
       <c r="G48" s="15">
-        <v>66.6</v>
+        <v>74.71</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0061833513377</v>
+        <v>0.0063379509217</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2964,16 +2958,16 @@
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F49" s="14">
-        <v>11740</v>
+        <v>1104</v>
       </c>
       <c r="G49" s="15">
-        <v>63.84</v>
+        <v>73</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0059271043454</v>
+        <v>0.0061928847181</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2996,13 +2990,13 @@
         <v>122</v>
       </c>
       <c r="F50" s="14">
-        <v>14240</v>
+        <v>9311</v>
       </c>
       <c r="G50" s="15">
-        <v>62.86</v>
+        <v>72.33</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0058361180944</v>
+        <v>0.0061360459131</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -3022,16 +3016,16 @@
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="F51" s="14">
-        <v>1595</v>
+        <v>4892</v>
       </c>
       <c r="G51" s="15">
-        <v>62.79</v>
+        <v>71.70</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0058296190765</v>
+        <v>0.0060826004697</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -3051,16 +3045,16 @@
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="F52" s="14">
-        <v>5123</v>
+        <v>3898</v>
       </c>
       <c r="G52" s="15">
-        <v>62.36</v>
+        <v>70.64</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0057896965379</v>
+        <v>0.0059926763902</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -3080,16 +3074,16 @@
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="F53" s="14">
-        <v>11251</v>
+        <v>5305</v>
       </c>
       <c r="G53" s="15">
-        <v>60.39</v>
+        <v>66.38</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0056067956049</v>
+        <v>0.0056312833916</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -3100,25 +3094,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="D54" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D54" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>45</v>
-      </c>
       <c r="F54" s="14">
-        <v>1155</v>
+        <v>14758</v>
       </c>
       <c r="G54" s="15">
-        <v>59.99</v>
+        <v>64.28</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0055696583596</v>
+        <v>0.0054531319134</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -3138,16 +3132,16 @@
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F55" s="14">
-        <v>1066</v>
+        <v>1195</v>
       </c>
       <c r="G55" s="15">
-        <v>59.46</v>
+        <v>63.74</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0055204515096</v>
+        <v>0.0054073215333</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3170,13 +3164,13 @@
         <v>136</v>
       </c>
       <c r="F56" s="14">
-        <v>850</v>
+        <v>5663</v>
       </c>
       <c r="G56" s="15">
-        <v>57.89</v>
+        <v>62.65</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0053746878219</v>
+        <v>0.0053148524327</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3196,16 +3190,16 @@
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="F57" s="14">
-        <v>8978</v>
+        <v>24704</v>
       </c>
       <c r="G57" s="15">
-        <v>57.28</v>
+        <v>61.68</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0053180535229</v>
+        <v>0.0052325634166</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3216,25 +3210,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="D58" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D58" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>142</v>
-      </c>
       <c r="F58" s="14">
-        <v>5464</v>
+        <v>878</v>
       </c>
       <c r="G58" s="15">
-        <v>55.99</v>
+        <v>60.41</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0051982859069</v>
+        <v>0.0051248241893</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3245,25 +3239,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="D59" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="D59" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>139</v>
-      </c>
       <c r="F59" s="14">
-        <v>3759</v>
+        <v>7637</v>
       </c>
       <c r="G59" s="15">
-        <v>55.77</v>
+        <v>58.79</v>
       </c>
       <c r="H59" s="16">
-        <v>0.005177860422</v>
+        <v>0.004987393049</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3283,16 +3277,16 @@
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F60" s="14">
-        <v>5548</v>
+        <v>3661</v>
       </c>
       <c r="G60" s="15">
-        <v>54.99</v>
+        <v>58.61</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0051054427937</v>
+        <v>0.0049721229223</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3312,16 +3306,16 @@
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F61" s="14">
-        <v>14179</v>
+        <v>14603</v>
       </c>
       <c r="G61" s="15">
-        <v>51.68</v>
+        <v>57.36</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0047981320891</v>
+        <v>0.0048660803757</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3341,16 +3335,16 @@
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="F62" s="14">
-        <v>12213</v>
+        <v>2265</v>
       </c>
       <c r="G62" s="15">
-        <v>51.60</v>
+        <v>57.08</v>
       </c>
       <c r="H62" s="16">
-        <v>0.00479070464</v>
+        <v>0.0048423268453</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3361,25 +3355,25 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="F63" s="14">
-        <v>657</v>
+        <v>2042</v>
       </c>
       <c r="G63" s="15">
-        <v>50.74</v>
+        <v>56.78</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0047108595627</v>
+        <v>0.0048168766341</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3390,25 +3384,25 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F64" s="14">
-        <v>989</v>
+        <v>1025</v>
       </c>
       <c r="G64" s="15">
-        <v>50.73</v>
+        <v>56.48</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0047099311316</v>
+        <v>0.004791426423</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3419,25 +3413,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>45</v>
+        <v>158</v>
       </c>
       <c r="F65" s="14">
-        <v>1970</v>
+        <v>11667</v>
       </c>
       <c r="G65" s="15">
-        <v>48.42</v>
+        <v>55.53</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0044954635401</v>
+        <v>0.0047108340876</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3448,25 +3442,25 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>159</v>
+        <v>22</v>
       </c>
       <c r="F66" s="14">
-        <v>2091</v>
+        <v>16857</v>
       </c>
       <c r="G66" s="15">
-        <v>47.84</v>
+        <v>53.67</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0044416145345</v>
+        <v>0.0045530427783</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3477,25 +3471,25 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F67" s="14">
-        <v>1088</v>
+        <v>12663</v>
       </c>
       <c r="G67" s="15">
-        <v>47.21</v>
+        <v>51.41</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0043831233732</v>
+        <v>0.0043613178542</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3506,25 +3500,25 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="F68" s="14">
-        <v>10477</v>
+        <v>4165</v>
       </c>
       <c r="G68" s="15">
-        <v>47.13</v>
+        <v>51.29</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0043756959241</v>
+        <v>0.0043511377697</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3535,25 +3529,25 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F69" s="14">
-        <v>776</v>
+        <v>1279</v>
       </c>
       <c r="G69" s="15">
-        <v>45.89</v>
+        <v>51.19</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0042605704638</v>
+        <v>0.004342654366</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3564,25 +3558,25 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F70" s="14">
-        <v>1242</v>
+        <v>376</v>
       </c>
       <c r="G70" s="15">
-        <v>45.51</v>
+        <v>50.44</v>
       </c>
       <c r="H70" s="16">
-        <v>0.0042252900808</v>
+        <v>0.0042790288381</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3593,25 +3587,25 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F71" s="14">
-        <v>3509</v>
+        <v>1129</v>
       </c>
       <c r="G71" s="15">
-        <v>45.12</v>
+        <v>48.65</v>
       </c>
       <c r="H71" s="16">
-        <v>0.0041890812666</v>
+        <v>0.0041271759114</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>13</v>
@@ -3622,25 +3616,25 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>172</v>
+        <v>58</v>
       </c>
       <c r="F72" s="14">
-        <v>741</v>
+        <v>3375</v>
       </c>
       <c r="G72" s="15">
-        <v>45</v>
+        <v>48.18</v>
       </c>
       <c r="H72" s="16">
-        <v>0.004177940093</v>
+        <v>0.0040873039139</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>13</v>
@@ -3651,25 +3645,25 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F73" s="14">
-        <v>16258</v>
+        <v>5727</v>
       </c>
       <c r="G73" s="15">
-        <v>42.45</v>
+        <v>46.79</v>
       </c>
       <c r="H73" s="16">
-        <v>0.0039411901544</v>
+        <v>0.0039693846022</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>13</v>
@@ -3680,25 +3674,25 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="F74" s="14">
-        <v>363</v>
+        <v>32497</v>
       </c>
       <c r="G74" s="15">
-        <v>41.96</v>
+        <v>46.14</v>
       </c>
       <c r="H74" s="16">
-        <v>0.003895697029</v>
+        <v>0.0039142424779</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>13</v>
@@ -3709,25 +3703,25 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="F75" s="14">
-        <v>31468</v>
+        <v>23461</v>
       </c>
       <c r="G75" s="15">
-        <v>40.43</v>
+        <v>44.53</v>
       </c>
       <c r="H75" s="16">
-        <v>0.0037536470658</v>
+        <v>0.003777659678</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>13</v>
@@ -3738,25 +3732,25 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F76" s="14">
-        <v>22685</v>
+        <v>5579</v>
       </c>
       <c r="G76" s="15">
-        <v>40.18</v>
+        <v>44.51</v>
       </c>
       <c r="H76" s="16">
-        <v>0.0037304362875</v>
+        <v>0.0037759629973</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>13</v>
@@ -3767,25 +3761,25 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>184</v>
+        <v>48</v>
       </c>
       <c r="F77" s="14">
-        <v>5382</v>
+        <v>10862</v>
       </c>
       <c r="G77" s="15">
-        <v>40.10</v>
+        <v>43.70</v>
       </c>
       <c r="H77" s="16">
-        <v>0.0037230088385</v>
+        <v>0.0037072474271</v>
       </c>
       <c r="I77" s="15" t="s">
         <v>13</v>
@@ -3796,25 +3790,25 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="F78" s="14">
-        <v>2006</v>
+        <v>1338</v>
       </c>
       <c r="G78" s="15">
-        <v>37.28</v>
+        <v>41.57</v>
       </c>
       <c r="H78" s="16">
-        <v>0.0034611912593</v>
+        <v>0.0035265509278</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>13</v>
@@ -3825,25 +3819,25 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>189</v>
+        <v>25</v>
       </c>
       <c r="F79" s="14">
-        <v>1291</v>
+        <v>803</v>
       </c>
       <c r="G79" s="15">
-        <v>37.07</v>
+        <v>40.7</v>
       </c>
       <c r="H79" s="16">
-        <v>0.0034416942055</v>
+        <v>0.0034527453154</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>13</v>
@@ -3854,25 +3848,25 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>192</v>
+        <v>17</v>
       </c>
       <c r="F80" s="14">
-        <v>3161</v>
+        <v>16106</v>
       </c>
       <c r="G80" s="15">
-        <v>35.44</v>
+        <v>40.19</v>
       </c>
       <c r="H80" s="16">
-        <v>0.003290359931</v>
+        <v>0.0034094799564</v>
       </c>
       <c r="I80" s="15" t="s">
         <v>13</v>
@@ -3892,16 +3886,16 @@
         <v>13</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="F81" s="14">
-        <v>2477</v>
+        <v>25643</v>
       </c>
       <c r="G81" s="15">
-        <v>35.27</v>
+        <v>39.26</v>
       </c>
       <c r="H81" s="16">
-        <v>0.0032745766018</v>
+        <v>0.0033305843018</v>
       </c>
       <c r="I81" s="15" t="s">
         <v>13</v>
@@ -3912,25 +3906,25 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="F82" s="14">
-        <v>24761</v>
+        <v>2568</v>
       </c>
       <c r="G82" s="15">
-        <v>34.98</v>
+        <v>39.04</v>
       </c>
       <c r="H82" s="16">
-        <v>0.003247652099</v>
+        <v>0.0033119208136</v>
       </c>
       <c r="I82" s="15" t="s">
         <v>13</v>
@@ -3950,16 +3944,16 @@
         <v>13</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="F83" s="14">
-        <v>6602</v>
+        <v>2080</v>
       </c>
       <c r="G83" s="15">
-        <v>33.88</v>
+        <v>39.01</v>
       </c>
       <c r="H83" s="16">
-        <v>0.0031455246745</v>
+        <v>0.0033093757925</v>
       </c>
       <c r="I83" s="15" t="s">
         <v>13</v>
@@ -3979,16 +3973,16 @@
         <v>13</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>17</v>
+        <v>202</v>
       </c>
       <c r="F84" s="14">
-        <v>15647</v>
+        <v>5570</v>
       </c>
       <c r="G84" s="15">
-        <v>33.39</v>
+        <v>38.25</v>
       </c>
       <c r="H84" s="16">
-        <v>0.003100031549</v>
+        <v>0.0032449019242</v>
       </c>
       <c r="I84" s="15" t="s">
         <v>13</v>
@@ -3999,25 +3993,25 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F85" s="14">
-        <v>2123</v>
+        <v>6846</v>
       </c>
       <c r="G85" s="15">
-        <v>33.25</v>
+        <v>37.23</v>
       </c>
       <c r="H85" s="16">
-        <v>0.0030870335132</v>
+        <v>0.0031583712062</v>
       </c>
       <c r="I85" s="15" t="s">
         <v>13</v>
@@ -4028,25 +4022,25 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="F86" s="14">
-        <v>112</v>
+        <v>2430</v>
       </c>
       <c r="G86" s="15">
-        <v>31.13</v>
+        <v>34.64</v>
       </c>
       <c r="H86" s="16">
-        <v>0.0028902061132</v>
+        <v>0.0029386510498</v>
       </c>
       <c r="I86" s="15" t="s">
         <v>13</v>
@@ -4057,25 +4051,25 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="F87" s="14">
-        <v>28922</v>
+        <v>116</v>
       </c>
       <c r="G87" s="15">
-        <v>29.27</v>
+        <v>34.33</v>
       </c>
       <c r="H87" s="16">
-        <v>0.0027175179227</v>
+        <v>0.0029123524982</v>
       </c>
       <c r="I87" s="15" t="s">
         <v>13</v>
@@ -4086,25 +4080,25 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="F88" s="14">
-        <v>5636</v>
+        <v>29321</v>
       </c>
       <c r="G88" s="15">
-        <v>28.90</v>
+        <v>33.65</v>
       </c>
       <c r="H88" s="16">
-        <v>0.0026831659708</v>
+        <v>0.0028546653529</v>
       </c>
       <c r="I88" s="15" t="s">
         <v>13</v>
@@ -4115,25 +4109,25 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="F89" s="14">
-        <v>2338</v>
+        <v>2194</v>
       </c>
       <c r="G89" s="15">
-        <v>28.16</v>
+        <v>33.50</v>
       </c>
       <c r="H89" s="16">
-        <v>0.0026144620671</v>
+        <v>0.0028419402473</v>
       </c>
       <c r="I89" s="15" t="s">
         <v>13</v>
@@ -4144,25 +4138,25 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="F90" s="14">
-        <v>28279</v>
+        <v>5793</v>
       </c>
       <c r="G90" s="15">
-        <v>26.38</v>
+        <v>32.06</v>
       </c>
       <c r="H90" s="16">
-        <v>0.0024492013256</v>
+        <v>0.0027197792337</v>
       </c>
       <c r="I90" s="15" t="s">
         <v>13</v>
@@ -4173,25 +4167,25 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
       <c r="B91" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>192</v>
+        <v>17</v>
       </c>
       <c r="F91" s="14">
-        <v>4959</v>
+        <v>29987</v>
       </c>
       <c r="G91" s="15">
-        <v>26.28</v>
+        <v>31.73</v>
       </c>
       <c r="H91" s="16">
-        <v>0.0024399170143</v>
+        <v>0.0026917840014</v>
       </c>
       <c r="I91" s="15" t="s">
         <v>13</v>
@@ -4202,25 +4196,25 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
       <c r="B92" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D92" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="F92" s="14">
-        <v>439</v>
+        <v>3304</v>
       </c>
       <c r="G92" s="15">
-        <v>25.79</v>
+        <v>31.35</v>
       </c>
       <c r="H92" s="16">
-        <v>0.0023944238889</v>
+        <v>0.0026595470673</v>
       </c>
       <c r="I92" s="15" t="s">
         <v>13</v>
@@ -4231,10 +4225,10 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
       <c r="B93" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D93" s="13" t="s">
         <v>13</v>
@@ -4243,13 +4237,13 @@
         <v>53</v>
       </c>
       <c r="F93" s="14">
-        <v>788</v>
+        <v>909</v>
       </c>
       <c r="G93" s="15">
-        <v>25.76</v>
+        <v>28.86</v>
       </c>
       <c r="H93" s="16">
-        <v>0.0023916385955</v>
+        <v>0.0024483103145</v>
       </c>
       <c r="I93" s="15" t="s">
         <v>13</v>
@@ -4260,25 +4254,25 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D94" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F94" s="14">
-        <v>2571</v>
+        <v>3148</v>
       </c>
       <c r="G94" s="15">
-        <v>25.65</v>
+        <v>27.30</v>
       </c>
       <c r="H94" s="16">
-        <v>0.002381425853</v>
+        <v>0.0023159692165</v>
       </c>
       <c r="I94" s="15" t="s">
         <v>13</v>
@@ -4289,25 +4283,25 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D95" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="F95" s="14">
-        <v>3187</v>
+        <v>456</v>
       </c>
       <c r="G95" s="15">
-        <v>25.23</v>
+        <v>27.23</v>
       </c>
       <c r="H95" s="16">
-        <v>0.0023424317455</v>
+        <v>0.0023100308338</v>
       </c>
       <c r="I95" s="15" t="s">
         <v>13</v>
@@ -4318,25 +4312,25 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D96" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F96" s="14">
-        <v>4482</v>
+        <v>2665</v>
       </c>
       <c r="G96" s="15">
-        <v>22.80</v>
+        <v>27.03</v>
       </c>
       <c r="H96" s="16">
-        <v>0.0021168229805</v>
+        <v>0.0022930640264</v>
       </c>
       <c r="I96" s="15" t="s">
         <v>13</v>
@@ -4347,25 +4341,25 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
       <c r="B97" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D97" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>60</v>
+        <v>202</v>
       </c>
       <c r="F97" s="14">
-        <v>3036</v>
+        <v>769</v>
       </c>
       <c r="G97" s="15">
-        <v>22.72</v>
+        <v>25.11</v>
       </c>
       <c r="H97" s="16">
-        <v>0.0021093955314</v>
+        <v>0.0021301826749</v>
       </c>
       <c r="I97" s="15" t="s">
         <v>13</v>
@@ -4376,25 +4370,25 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D98" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="F98" s="14">
-        <v>14989</v>
+        <v>5129</v>
       </c>
       <c r="G98" s="15">
-        <v>22.62</v>
+        <v>24.77</v>
       </c>
       <c r="H98" s="16">
-        <v>0.0021001112201</v>
+        <v>0.0021013391022</v>
       </c>
       <c r="I98" s="15" t="s">
         <v>13</v>
@@ -4405,25 +4399,25 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D99" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="F99" s="14">
-        <v>10781</v>
+        <v>75</v>
       </c>
       <c r="G99" s="15">
-        <v>22.43</v>
+        <v>23.56</v>
       </c>
       <c r="H99" s="16">
-        <v>0.0020824710286</v>
+        <v>0.0019986899172</v>
       </c>
       <c r="I99" s="15" t="s">
         <v>13</v>
@@ -4434,25 +4428,25 @@
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
       <c r="B100" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D100" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F100" s="14">
-        <v>26546</v>
+        <v>4648</v>
       </c>
       <c r="G100" s="15">
-        <v>21.38</v>
+        <v>22.68</v>
       </c>
       <c r="H100" s="16">
-        <v>0.0019849857597</v>
+        <v>0.0019240359644</v>
       </c>
       <c r="I100" s="15" t="s">
         <v>13</v>
@@ -4463,25 +4457,25 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
       <c r="B101" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D101" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>236</v>
+        <v>122</v>
       </c>
       <c r="F101" s="14">
-        <v>2530</v>
+        <v>3401</v>
       </c>
       <c r="G101" s="15">
-        <v>20.80</v>
+        <v>22.53</v>
       </c>
       <c r="H101" s="16">
-        <v>0.0019311367541</v>
+        <v>0.0019113108588</v>
       </c>
       <c r="I101" s="15" t="s">
         <v>13</v>
@@ -4501,16 +4495,16 @@
         <v>13</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>197</v>
+        <v>48</v>
       </c>
       <c r="F102" s="14">
-        <v>72</v>
+        <v>15539</v>
       </c>
       <c r="G102" s="15">
-        <v>20.68</v>
+        <v>21.59</v>
       </c>
       <c r="H102" s="16">
-        <v>0.0019199955805</v>
+        <v>0.0018315668638</v>
       </c>
       <c r="I102" s="15" t="s">
         <v>13</v>
@@ -4533,13 +4527,13 @@
         <v>53</v>
       </c>
       <c r="F103" s="14">
-        <v>2099</v>
+        <v>2172</v>
       </c>
       <c r="G103" s="15">
-        <v>20.37</v>
+        <v>20.20</v>
       </c>
       <c r="H103" s="16">
-        <v>0.0018912142154</v>
+        <v>0.0017136475521</v>
       </c>
       <c r="I103" s="15" t="s">
         <v>13</v>
@@ -4559,16 +4553,16 @@
         <v>13</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>139</v>
+        <v>45</v>
       </c>
       <c r="F104" s="14">
-        <v>3275</v>
+        <v>1055</v>
       </c>
       <c r="G104" s="15">
-        <v>20.17</v>
+        <v>19.49</v>
       </c>
       <c r="H104" s="16">
-        <v>0.0018726455928</v>
+        <v>0.0016534153856</v>
       </c>
       <c r="I104" s="15" t="s">
         <v>13</v>
@@ -4588,16 +4582,16 @@
         <v>13</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>17</v>
+        <v>202</v>
       </c>
       <c r="F105" s="14">
-        <v>16207</v>
+        <v>778</v>
       </c>
       <c r="G105" s="15">
-        <v>18.72</v>
+        <v>19.28</v>
       </c>
       <c r="H105" s="16">
-        <v>0.0017380230787</v>
+        <v>0.0016356002378</v>
       </c>
       <c r="I105" s="15" t="s">
         <v>13</v>
@@ -4617,16 +4611,16 @@
         <v>13</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="F106" s="14">
-        <v>1862</v>
+        <v>1930</v>
       </c>
       <c r="G106" s="15">
-        <v>15.74</v>
+        <v>18.42</v>
       </c>
       <c r="H106" s="16">
-        <v>0.0014613506014</v>
+        <v>0.0015626429658</v>
       </c>
       <c r="I106" s="15" t="s">
         <v>13</v>
@@ -4646,16 +4640,16 @@
         <v>13</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="F107" s="14">
-        <v>2325</v>
+        <v>3382</v>
       </c>
       <c r="G107" s="15">
-        <v>14.95</v>
+        <v>11.26</v>
       </c>
       <c r="H107" s="16">
-        <v>0.001388004542</v>
+        <v>0.0009552312592</v>
       </c>
       <c r="I107" s="15" t="s">
         <v>13</v>
@@ -4675,16 +4669,16 @@
         <v>13</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>236</v>
+        <v>48</v>
       </c>
       <c r="F108" s="14">
-        <v>7810</v>
+        <v>8090</v>
       </c>
       <c r="G108" s="15">
-        <v>12.73</v>
+        <v>9.87</v>
       </c>
       <c r="H108" s="16">
-        <v>0.0011818928307</v>
+        <v>0.0008373119475</v>
       </c>
       <c r="I108" s="15" t="s">
         <v>13</v>
@@ -5199,10 +5193,10 @@
         <v>13</v>
       </c>
       <c r="G136" s="9">
-        <v>2.64</v>
+        <v>6.56</v>
       </c>
       <c r="H136" s="10">
-        <v>0.0002451058187</v>
+        <v>0.0005565112842</v>
       </c>
       <c r="I136" s="9" t="s">
         <v>13</v>
@@ -5236,21 +5230,21 @@
         <v>13</v>
       </c>
       <c r="G138" s="18">
-        <v>0.45812560000376834</v>
-      </c>
-      <c r="H138" s="16" t="s">
-        <v>266</v>
+        <v>9.341445299989573</v>
+      </c>
+      <c r="H138" s="19">
+        <v>0.0007924725184029687</v>
       </c>
       <c r="I138" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="J138" s="19" t="s">
+      <c r="J138" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="139" spans="2:10" ht="15" customHeight="1">
       <c r="B139" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C139" s="18" t="s">
         <v>13</v>
@@ -5265,21 +5259,21 @@
         <v>13</v>
       </c>
       <c r="G139" s="18">
-        <v>10770.8581256</v>
-      </c>
-      <c r="H139" s="20">
-        <v>0.9999999999945314</v>
+        <v>11787.7214453</v>
+      </c>
+      <c r="H139" s="19">
+        <v>0.9999999999949031</v>
       </c>
       <c r="I139" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="J139" s="19" t="s">
+      <c r="J139" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="142" spans="2:9" ht="15" customHeight="1">
       <c r="B142" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C142" s="21"/>
       <c r="D142" s="21"/>
@@ -5291,7 +5285,7 @@
     </row>
     <row r="143" spans="2:8" ht="15" customHeight="1">
       <c r="B143" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C143" s="21"/>
       <c r="D143" s="21"/>
@@ -5300,9 +5294,9 @@
       <c r="G143" s="21"/>
       <c r="H143" s="21"/>
     </row>
-    <row r="144" spans="2:8" ht="15" customHeight="1">
-      <c r="B144" s="13" t="s">
-        <v>270</v>
+    <row r="144" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B144" s="22" t="s">
+        <v>269</v>
       </c>
       <c r="C144" s="21"/>
       <c r="D144" s="21"/>
@@ -5313,7 +5307,7 @@
     </row>
     <row r="145" spans="2:8" ht="27.6" customHeight="1">
       <c r="B145" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C145" s="21"/>
       <c r="D145" s="21"/>
@@ -5324,7 +5318,7 @@
     </row>
     <row r="146" spans="2:8" ht="27.6" customHeight="1">
       <c r="B146" s="22" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C146" s="21"/>
       <c r="D146" s="21"/>
@@ -5333,50 +5327,38 @@
       <c r="G146" s="21"/>
       <c r="H146" s="21"/>
     </row>
-    <row r="147" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B147" s="22" t="s">
+    <row r="148" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B148" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="C148" s="21"/>
+      <c r="D148" s="21"/>
+      <c r="E148" s="21"/>
+      <c r="F148" s="21"/>
+      <c r="G148" s="21"/>
+      <c r="H148" s="21"/>
+    </row>
+    <row r="151" ht="15">
+      <c r="B151" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="C147" s="21"/>
-      <c r="D147" s="21"/>
-      <c r="E147" s="21"/>
-      <c r="F147" s="21"/>
-      <c r="G147" s="21"/>
-      <c r="H147" s="21"/>
-    </row>
-    <row r="149" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B149" s="22" t="s">
+    </row>
+    <row r="166" ht="15">
+      <c r="B166" s="21" t="s">
         <v>274</v>
-      </c>
-      <c r="C149" s="21"/>
-      <c r="D149" s="21"/>
-      <c r="E149" s="21"/>
-      <c r="F149" s="21"/>
-      <c r="G149" s="21"/>
-      <c r="H149" s="21"/>
-    </row>
-    <row r="152" ht="15">
-      <c r="B152" s="21" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="167" ht="15">
       <c r="B167" s="21" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="168" ht="15">
-      <c r="B168" s="21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="B144:H144"/>
     <mergeCell ref="B145:H145"/>
     <mergeCell ref="B146:H146"/>
-    <mergeCell ref="B147:H147"/>
-    <mergeCell ref="B149:H149"/>
+    <mergeCell ref="B148:H148"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
